--- a/Dday 검증용 엑셀.xlsx
+++ b/Dday 검증용 엑셀.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2. Git\AndroidApp_Dday\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44701FD1-FE06-4A33-B2B5-5FBAFE7071E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09B4870-26E1-4312-B2FA-C9EAC4ADAF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9840" yWindow="3180" windowWidth="11895" windowHeight="11970" xr2:uid="{8CA68E9B-9CD2-4861-B188-157A23DF58F8}"/>
+    <workbookView xWindow="3045" yWindow="1785" windowWidth="15720" windowHeight="11970" activeTab="1" xr2:uid="{8CA68E9B-9CD2-4861-B188-157A23DF58F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,25 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
-  <si>
-    <t>공휴일 날짜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>계산</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시작일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
   <si>
     <t>종료일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주말</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -70,12 +55,40 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>당일 날짜 포함</t>
+    <t>테스트 날짜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>당일날짜 미포함</t>
+    <t>당일 날짜 포함 총일수</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당일날짜 미포함 총일수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일 특징 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>날짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 디데이</t>
+  </si>
+  <si>
+    <t>전체 디데이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주말 제외, 공휴일 제외</t>
+  </si>
+  <si>
+    <t>주말 포함, 공휴일 제외</t>
+  </si>
+  <si>
+    <t>주말 제외, 공휴일 포함</t>
   </si>
 </sst>
 </file>
@@ -462,202 +475,1707 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B91344-3E73-4DAE-AF73-D2F33729720D}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.25" customWidth="1"/>
-    <col min="4" max="4" width="21.25" customWidth="1"/>
-    <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B1" s="1">
+        <v>46026</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>46071</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46032</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46026</v>
+      </c>
+      <c r="E2" t="str">
+        <f>IF(COUNTIF(A:A, D2)&gt;0, "공휴일", IF(COUNTIF(B:B, D2)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F2">
+        <f>F3+1</f>
+        <v>55</v>
+      </c>
+      <c r="G2">
+        <f>IF(E2="주말",G3+0,IF(E2="공휴일",G3+0,G3+1))</f>
+        <v>37</v>
+      </c>
+      <c r="H2">
+        <f>IF(E2="주말",H3+1,IF(E2="공휴일",H3+0, H3+1))</f>
+        <v>52</v>
+      </c>
+      <c r="I2">
+        <f>IF(E2="주말",I3+0,IF(E2="공휴일",I3+1, I3+1))</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B3" s="1">
+        <f t="shared" ref="B3:B16" si="0">B1+7</f>
+        <v>46033</v>
+      </c>
+      <c r="D3" s="1">
+        <v>46027</v>
+      </c>
+      <c r="E3" t="str">
+        <f>IF(COUNTIF(A:A, D3)&gt;0, "공휴일", IF(COUNTIF(B:B, D3)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F3">
+        <f>F4+1</f>
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <f>IF(E3="주말",G4+0,IF(E3="공휴일",G4+0, G4+1))</f>
+        <v>37</v>
+      </c>
+      <c r="H3">
+        <f>IF(E3="주말",H4+1,IF(E3="공휴일",H4+0, H4+1))</f>
+        <v>51</v>
+      </c>
+      <c r="I3">
+        <f>IF(E3="주말",I4+0,IF(E3="공휴일",I4+1, I4+1))</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1">
+        <f t="shared" si="0"/>
+        <v>46039</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46028</v>
+      </c>
+      <c r="E4" t="str">
+        <f>IF(COUNTIF(A:A, D4)&gt;0, "공휴일", IF(COUNTIF(B:B, D4)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F4">
+        <f>F5+1</f>
+        <v>53</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4:G56" si="1">IF(E4="주말",G5+0,IF(E4="공휴일",G5+0, G5+1))</f>
+        <v>36</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H56" si="2">IF(E4="주말",H5+1,IF(E4="공휴일",H5+0, H5+1))</f>
+        <v>50</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I56" si="3">IF(E4="주말",I5+0,IF(E4="공휴일",I5+1, I5+1))</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <f t="shared" si="0"/>
+        <v>46040</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46029</v>
+      </c>
+      <c r="E5" t="str">
+        <f>IF(COUNTIF(A:A, D5)&gt;0, "공휴일", IF(COUNTIF(B:B, D5)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F5">
+        <f>F6+1</f>
+        <v>52</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <f t="shared" si="0"/>
+        <v>46046</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46030</v>
+      </c>
+      <c r="E6" t="str">
+        <f>IF(COUNTIF(A:A, D6)&gt;0, "공휴일", IF(COUNTIF(B:B, D6)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F6">
+        <f>F7+1</f>
+        <v>51</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>46047</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46031</v>
+      </c>
+      <c r="E7" t="str">
+        <f>IF(COUNTIF(A:A, D7)&gt;0, "공휴일", IF(COUNTIF(B:B, D7)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F7">
+        <f>F8+1</f>
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <f t="shared" si="0"/>
+        <v>46053</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46032</v>
+      </c>
+      <c r="E8" t="str">
+        <f>IF(COUNTIF(A:A, D8)&gt;0, "공휴일", IF(COUNTIF(B:B, D8)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F8">
+        <f>F9+1</f>
+        <v>49</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>46054</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46033</v>
+      </c>
+      <c r="E9" t="str">
+        <f>IF(COUNTIF(A:A, D9)&gt;0, "공휴일", IF(COUNTIF(B:B, D9)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F9">
+        <f>F10+1</f>
+        <v>48</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>46060</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46034</v>
+      </c>
+      <c r="E10" t="str">
+        <f>IF(COUNTIF(A:A, D10)&gt;0, "공휴일", IF(COUNTIF(B:B, D10)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F10">
+        <f>F11+1</f>
+        <v>47</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <f t="shared" si="0"/>
+        <v>46061</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46035</v>
+      </c>
+      <c r="E11" t="str">
+        <f>IF(COUNTIF(A:A, D11)&gt;0, "공휴일", IF(COUNTIF(B:B, D11)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F11">
+        <f>F12+1</f>
+        <v>46</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>46067</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46036</v>
+      </c>
+      <c r="E12" t="str">
+        <f>IF(COUNTIF(A:A, D12)&gt;0, "공휴일", IF(COUNTIF(B:B, D12)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F12">
+        <f>F13+1</f>
+        <v>45</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <f t="shared" si="0"/>
+        <v>46068</v>
+      </c>
+      <c r="D13" s="1">
+        <v>46037</v>
+      </c>
+      <c r="E13" t="str">
+        <f>IF(COUNTIF(A:A, D13)&gt;0, "공휴일", IF(COUNTIF(B:B, D13)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F13">
+        <f>F14+1</f>
+        <v>44</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <f t="shared" si="0"/>
+        <v>46074</v>
+      </c>
+      <c r="D14" s="1">
+        <v>46038</v>
+      </c>
+      <c r="E14" t="str">
+        <f>IF(COUNTIF(A:A, D14)&gt;0, "공휴일", IF(COUNTIF(B:B, D14)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F14">
+        <f>F15+1</f>
+        <v>43</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <f t="shared" si="0"/>
+        <v>46075</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46039</v>
+      </c>
+      <c r="E15" t="str">
+        <f>IF(COUNTIF(A:A, D15)&gt;0, "공휴일", IF(COUNTIF(B:B, D15)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F15">
+        <f>F16+1</f>
+        <v>42</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
+        <f t="shared" si="0"/>
+        <v>46081</v>
+      </c>
+      <c r="D16" s="1">
+        <v>46040</v>
+      </c>
+      <c r="E16" t="str">
+        <f>IF(COUNTIF(A:A, D16)&gt;0, "공휴일", IF(COUNTIF(B:B, D16)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F16">
+        <f>F17+1</f>
+        <v>41</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D17" s="1">
+        <v>46041</v>
+      </c>
+      <c r="E17" t="str">
+        <f>IF(COUNTIF(A:A, D17)&gt;0, "공휴일", IF(COUNTIF(B:B, D17)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F17">
+        <f>F18+1</f>
+        <v>40</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D18" s="1">
+        <v>46042</v>
+      </c>
+      <c r="E18" t="str">
+        <f>IF(COUNTIF(A:A, D18)&gt;0, "공휴일", IF(COUNTIF(B:B, D18)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F18">
+        <f>F19+1</f>
+        <v>39</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D19" s="1">
+        <v>46043</v>
+      </c>
+      <c r="E19" t="str">
+        <f>IF(COUNTIF(A:A, D19)&gt;0, "공휴일", IF(COUNTIF(B:B, D19)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F19">
+        <f>F20+1</f>
+        <v>38</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D20" s="1">
+        <v>46044</v>
+      </c>
+      <c r="E20" t="str">
+        <f>IF(COUNTIF(A:A, D20)&gt;0, "공휴일", IF(COUNTIF(B:B, D20)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F20">
+        <f>F21+1</f>
+        <v>37</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D21" s="1">
+        <v>46045</v>
+      </c>
+      <c r="E21" t="str">
+        <f>IF(COUNTIF(A:A, D21)&gt;0, "공휴일", IF(COUNTIF(B:B, D21)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F21">
+        <f>F22+1</f>
+        <v>36</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D22" s="1">
+        <v>46046</v>
+      </c>
+      <c r="E22" t="str">
+        <f>IF(COUNTIF(A:A, D22)&gt;0, "공휴일", IF(COUNTIF(B:B, D22)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F22">
+        <f>F23+1</f>
+        <v>35</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D23" s="1">
+        <v>46047</v>
+      </c>
+      <c r="E23" t="str">
+        <f>IF(COUNTIF(A:A, D23)&gt;0, "공휴일", IF(COUNTIF(B:B, D23)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F23">
+        <f>F24+1</f>
+        <v>34</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D24" s="1">
+        <v>46048</v>
+      </c>
+      <c r="E24" t="str">
+        <f>IF(COUNTIF(A:A, D24)&gt;0, "공휴일", IF(COUNTIF(B:B, D24)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F24">
+        <f>F25+1</f>
+        <v>33</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D25" s="1">
+        <v>46049</v>
+      </c>
+      <c r="E25" t="str">
+        <f>IF(COUNTIF(A:A, D25)&gt;0, "공휴일", IF(COUNTIF(B:B, D25)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F25">
+        <f>F26+1</f>
+        <v>32</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D26" s="1">
+        <v>46050</v>
+      </c>
+      <c r="E26" t="str">
+        <f>IF(COUNTIF(A:A, D26)&gt;0, "공휴일", IF(COUNTIF(B:B, D26)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F26">
+        <f>F27+1</f>
+        <v>31</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D27" s="1">
+        <v>46051</v>
+      </c>
+      <c r="E27" t="str">
+        <f>IF(COUNTIF(A:A, D27)&gt;0, "공휴일", IF(COUNTIF(B:B, D27)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F27">
+        <f>F28+1</f>
+        <v>30</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D28" s="1">
+        <v>46052</v>
+      </c>
+      <c r="E28" t="str">
+        <f>IF(COUNTIF(A:A, D28)&gt;0, "공휴일", IF(COUNTIF(B:B, D28)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F28">
+        <f>F29+1</f>
+        <v>29</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D29" s="1">
+        <v>46053</v>
+      </c>
+      <c r="E29" t="str">
+        <f>IF(COUNTIF(A:A, D29)&gt;0, "공휴일", IF(COUNTIF(B:B, D29)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F29">
+        <f>F30+1</f>
+        <v>28</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D30" s="1">
+        <v>46054</v>
+      </c>
+      <c r="E30" t="str">
+        <f>IF(COUNTIF(A:A, D30)&gt;0, "공휴일", IF(COUNTIF(B:B, D30)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F30">
+        <f>F31+1</f>
+        <v>27</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D31" s="1">
+        <v>46055</v>
+      </c>
+      <c r="E31" t="str">
+        <f>IF(COUNTIF(A:A, D31)&gt;0, "공휴일", IF(COUNTIF(B:B, D31)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F31">
+        <f>F32+1</f>
+        <v>26</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D32" s="1">
+        <v>46056</v>
+      </c>
+      <c r="E32" t="str">
+        <f>IF(COUNTIF(A:A, D32)&gt;0, "공휴일", IF(COUNTIF(B:B, D32)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F32">
+        <f>F33+1</f>
+        <v>25</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D33" s="1">
+        <v>46057</v>
+      </c>
+      <c r="E33" t="str">
+        <f>IF(COUNTIF(A:A, D33)&gt;0, "공휴일", IF(COUNTIF(B:B, D33)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F33">
+        <f>F34+1</f>
+        <v>24</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D34" s="1">
+        <v>46058</v>
+      </c>
+      <c r="E34" t="str">
+        <f>IF(COUNTIF(A:A, D34)&gt;0, "공휴일", IF(COUNTIF(B:B, D34)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F34">
+        <f>F35+1</f>
+        <v>23</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D35" s="1">
+        <v>46059</v>
+      </c>
+      <c r="E35" t="str">
+        <f>IF(COUNTIF(A:A, D35)&gt;0, "공휴일", IF(COUNTIF(B:B, D35)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F35">
+        <f>F36+1</f>
+        <v>22</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D36" s="1">
+        <v>46060</v>
+      </c>
+      <c r="E36" t="str">
+        <f>IF(COUNTIF(A:A, D36)&gt;0, "공휴일", IF(COUNTIF(B:B, D36)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F36">
+        <f>F37+1</f>
+        <v>21</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D37" s="1">
+        <v>46061</v>
+      </c>
+      <c r="E37" t="str">
+        <f>IF(COUNTIF(A:A, D37)&gt;0, "공휴일", IF(COUNTIF(B:B, D37)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F37">
+        <f>F38+1</f>
+        <v>20</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D38" s="1">
+        <v>46062</v>
+      </c>
+      <c r="E38" t="str">
+        <f>IF(COUNTIF(A:A, D38)&gt;0, "공휴일", IF(COUNTIF(B:B, D38)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F38">
+        <f>F39+1</f>
+        <v>19</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D39" s="1">
+        <v>46063</v>
+      </c>
+      <c r="E39" t="str">
+        <f>IF(COUNTIF(A:A, D39)&gt;0, "공휴일", IF(COUNTIF(B:B, D39)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F39">
+        <f>F40+1</f>
+        <v>18</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D40" s="1">
+        <v>46064</v>
+      </c>
+      <c r="E40" t="str">
+        <f>IF(COUNTIF(A:A, D40)&gt;0, "공휴일", IF(COUNTIF(B:B, D40)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F40">
+        <f>F41+1</f>
+        <v>17</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D41" s="1">
+        <v>46065</v>
+      </c>
+      <c r="E41" t="str">
+        <f>IF(COUNTIF(A:A, D41)&gt;0, "공휴일", IF(COUNTIF(B:B, D41)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F41">
+        <f>F42+1</f>
+        <v>16</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D42" s="1">
+        <v>46066</v>
+      </c>
+      <c r="E42" t="str">
+        <f>IF(COUNTIF(A:A, D42)&gt;0, "공휴일", IF(COUNTIF(B:B, D42)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F42">
+        <f>F43+1</f>
+        <v>15</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D43" s="1">
+        <v>46067</v>
+      </c>
+      <c r="E43" t="str">
+        <f>IF(COUNTIF(A:A, D43)&gt;0, "공휴일", IF(COUNTIF(B:B, D43)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F43">
+        <f>F44+1</f>
+        <v>14</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D44" s="1">
+        <v>46068</v>
+      </c>
+      <c r="E44" t="str">
+        <f>IF(COUNTIF(A:A, D44)&gt;0, "공휴일", IF(COUNTIF(B:B, D44)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F44">
+        <f>F45+1</f>
+        <v>13</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D45" s="1">
+        <v>46069</v>
+      </c>
+      <c r="E45" t="str">
+        <f>IF(COUNTIF(A:A, D45)&gt;0, "공휴일", IF(COUNTIF(B:B, D45)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F45">
+        <f>F46+1</f>
+        <v>12</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D46" s="1">
+        <v>46070</v>
+      </c>
+      <c r="E46" t="str">
+        <f>IF(COUNTIF(A:A, D46)&gt;0, "공휴일", IF(COUNTIF(B:B, D46)&gt;0, "주말", "평일"))</f>
+        <v>공휴일</v>
+      </c>
+      <c r="F46">
+        <f>F47+1</f>
+        <v>11</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D47" s="1">
+        <v>46071</v>
+      </c>
+      <c r="E47" t="str">
+        <f>IF(COUNTIF(A:A, D47)&gt;0, "공휴일", IF(COUNTIF(B:B, D47)&gt;0, "주말", "평일"))</f>
+        <v>공휴일</v>
+      </c>
+      <c r="F47">
+        <f>F48+1</f>
+        <v>10</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D48" s="1">
+        <v>46072</v>
+      </c>
+      <c r="E48" t="str">
+        <f>IF(COUNTIF(A:A, D48)&gt;0, "공휴일", IF(COUNTIF(B:B, D48)&gt;0, "주말", "평일"))</f>
+        <v>공휴일</v>
+      </c>
+      <c r="F48">
+        <f>F49+1</f>
+        <v>9</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D49" s="1">
+        <v>46073</v>
+      </c>
+      <c r="E49" t="str">
+        <f>IF(COUNTIF(A:A, D49)&gt;0, "공휴일", IF(COUNTIF(B:B, D49)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F49">
+        <f>F50+1</f>
+        <v>8</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D50" s="1">
+        <v>46074</v>
+      </c>
+      <c r="E50" t="str">
+        <f>IF(COUNTIF(A:A, D50)&gt;0, "공휴일", IF(COUNTIF(B:B, D50)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F50">
+        <f>F51+1</f>
+        <v>7</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D51" s="1">
+        <v>46075</v>
+      </c>
+      <c r="E51" t="str">
+        <f>IF(COUNTIF(A:A, D51)&gt;0, "공휴일", IF(COUNTIF(B:B, D51)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F51">
+        <f>F52+1</f>
+        <v>6</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D52" s="1">
+        <v>46076</v>
+      </c>
+      <c r="E52" t="str">
+        <f>IF(COUNTIF(A:A, D52)&gt;0, "공휴일", IF(COUNTIF(B:B, D52)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F52">
+        <f>F53+1</f>
+        <v>5</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D53" s="1">
+        <v>46077</v>
+      </c>
+      <c r="E53" t="str">
+        <f>IF(COUNTIF(A:A, D53)&gt;0, "공휴일", IF(COUNTIF(B:B, D53)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F53">
+        <f>F54+1</f>
+        <v>4</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D54" s="1">
+        <v>46078</v>
+      </c>
+      <c r="E54" t="str">
+        <f>IF(COUNTIF(A:A, D54)&gt;0, "공휴일", IF(COUNTIF(B:B, D54)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F54">
+        <f>F55+1</f>
+        <v>3</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D55" s="1">
+        <v>46079</v>
+      </c>
+      <c r="E55" t="str">
+        <f>IF(COUNTIF(A:A, D55)&gt;0, "공휴일", IF(COUNTIF(B:B, D55)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F55">
+        <f>F56+1</f>
+        <v>2</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D56" s="1">
+        <v>46080</v>
+      </c>
+      <c r="E56" t="str">
+        <f>IF(COUNTIF(A:A, D56)&gt;0, "공휴일", IF(COUNTIF(B:B, D56)&gt;0, "주말", "평일"))</f>
+        <v>평일</v>
+      </c>
+      <c r="F56">
+        <f>F57+1</f>
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <f>IF(E56="주말",G57+0,IF(E56="공휴일",G57+0, G57+1))</f>
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D57" s="1">
+        <v>46081</v>
+      </c>
+      <c r="E57" t="str">
+        <f>IF(COUNTIF(A:A, D57)&gt;0, "공휴일", IF(COUNTIF(B:B, D57)&gt;0, "주말", "평일"))</f>
+        <v>주말</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6AC53DF-165D-438D-AAE8-9A9D75FD71F1}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.125" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+    <col min="4" max="4" width="22.75" customWidth="1"/>
+    <col min="5" max="5" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1">
+        <v>46026</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1">
+        <v>46027</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" s="1">
+        <v>46081</v>
+      </c>
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <f>NETWORKDAYS.INTL(B1,B2, "0000000")</f>
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <f>NETWORKDAYS.INTL(E1,E2, "0000000")</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>NETWORKDAYS(B1,B2, Sheet1!A:A)</f>
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <f>NETWORKDAYS(E1,E2, Sheet1!A:A)</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>46071</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>46072</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1">
-        <v>46081</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <f>NETWORKDAYS.INTL(B1,B2, "0000000", Sheet1!A:A)</f>
+        <v>53</v>
+      </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <f>NETWORKDAYS.INTL(E1,E2, "0000000", Sheet1!A:A)</f>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>NETWORKDAYS.INTL(B1,B2,1)</f>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <f>NETWORKDAYS(E3, E4, A2:A6)</f>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>46026</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8">
-        <f>NETWORKDAYS.INTL(E3,E4, "0000000", A2:A5)</f>
-        <v>53</v>
+        <f>NETWORKDAYS.INTL(E1,E2,1)</f>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>46032</v>
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <f>NETWORKDAYS.INTL(B1+1,B2, "0000000")</f>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
       </c>
       <c r="E9">
-        <f>NETWORKDAYS.INTL(E3,E4,1)</f>
+        <f>NETWORKDAYS.INTL(E1+1,E2, "0000000")</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <f>NETWORKDAYS(B1+1,B2, Sheet1!A:A)</f>
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <f>NETWORKDAYS(E1+1,E2, Sheet1!A:A)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <f>NETWORKDAYS.INTL(B1+1,B2, "0000000", Sheet1!A:A)</f>
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <f>NETWORKDAYS.INTL(E1+1,E2, "0000000", Sheet1!A:A)</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <f>NETWORKDAYS.INTL(B1+1,B2,1)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <f t="shared" ref="A10:A23" si="0">A8+7</f>
-        <v>46033</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <f t="shared" si="0"/>
-        <v>46039</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <f>NETWORKDAYS.INTL(E1+1,E2,1)</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <f t="shared" si="0"/>
-        <v>46040</v>
-      </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12">
-        <f>E7-1</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <f t="shared" si="0"/>
-        <v>46046</v>
-      </c>
-      <c r="D13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <f t="shared" ref="E13:E14" si="1">E8-1</f>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <f t="shared" si="0"/>
-        <v>46047</v>
-      </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
       <c r="E14">
-        <f t="shared" si="1"/>
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <f t="shared" si="0"/>
-        <v>46053</v>
+      <c r="B15" s="1"/>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15">
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <f t="shared" si="0"/>
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <f t="shared" si="0"/>
-        <v>46060</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <f t="shared" si="0"/>
-        <v>46061</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <f t="shared" si="0"/>
-        <v>46067</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <f t="shared" si="0"/>
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <f t="shared" si="0"/>
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <f t="shared" si="0"/>
-        <v>46075</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <f t="shared" si="0"/>
-        <v>46081</v>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Dday 검증용 엑셀.xlsx
+++ b/Dday 검증용 엑셀.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2. Git\AndroidApp_Dday\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09B4870-26E1-4312-B2FA-C9EAC4ADAF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AFF6D9-6A95-42BA-A4D1-E69C78CDF164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="1785" windowWidth="15720" windowHeight="11970" activeTab="1" xr2:uid="{8CA68E9B-9CD2-4861-B188-157A23DF58F8}"/>
+    <workbookView xWindow="13395" yWindow="2790" windowWidth="15720" windowHeight="11970" xr2:uid="{8CA68E9B-9CD2-4861-B188-157A23DF58F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="14">
   <si>
     <t>종료일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -521,11 +521,11 @@
         <v>46026</v>
       </c>
       <c r="E2" t="str">
-        <f>IF(COUNTIF(A:A, D2)&gt;0, "공휴일", IF(COUNTIF(B:B, D2)&gt;0, "주말", "평일"))</f>
+        <f t="shared" ref="E2:E33" si="0">IF(COUNTIF(A:A, D2)&gt;0, "공휴일", IF(COUNTIF(B:B, D2)&gt;0, "주말", "평일"))</f>
         <v>주말</v>
       </c>
       <c r="F2">
-        <f>F3+1</f>
+        <f t="shared" ref="F2:F33" si="1">F3+1</f>
         <v>55</v>
       </c>
       <c r="G2">
@@ -546,18 +546,18 @@
         <v>46072</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B16" si="0">B1+7</f>
+        <f t="shared" ref="B3:B16" si="2">B1+7</f>
         <v>46033</v>
       </c>
       <c r="D3" s="1">
         <v>46027</v>
       </c>
       <c r="E3" t="str">
-        <f>IF(COUNTIF(A:A, D3)&gt;0, "공휴일", IF(COUNTIF(B:B, D3)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F3">
-        <f>F4+1</f>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="G3">
@@ -576,378 +576,378 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46039</v>
       </c>
       <c r="D4" s="1">
         <v>46028</v>
       </c>
       <c r="E4" t="str">
-        <f>IF(COUNTIF(A:A, D4)&gt;0, "공휴일", IF(COUNTIF(B:B, D4)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F4">
-        <f>F5+1</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G56" si="1">IF(E4="주말",G5+0,IF(E4="공휴일",G5+0, G5+1))</f>
+        <f t="shared" ref="G4:G55" si="3">IF(E4="주말",G5+0,IF(E4="공휴일",G5+0, G5+1))</f>
         <v>36</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H56" si="2">IF(E4="주말",H5+1,IF(E4="공휴일",H5+0, H5+1))</f>
+        <f t="shared" ref="H4:H56" si="4">IF(E4="주말",H5+1,IF(E4="공휴일",H5+0, H5+1))</f>
         <v>50</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I56" si="3">IF(E4="주말",I5+0,IF(E4="공휴일",I5+1, I5+1))</f>
+        <f t="shared" ref="I4:I56" si="5">IF(E4="주말",I5+0,IF(E4="공휴일",I5+1, I5+1))</f>
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46040</v>
       </c>
       <c r="D5" s="1">
         <v>46029</v>
       </c>
       <c r="E5" t="str">
-        <f>IF(COUNTIF(A:A, D5)&gt;0, "공휴일", IF(COUNTIF(B:B, D5)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F5">
-        <f>F6+1</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="G5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="H5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>49</v>
       </c>
       <c r="I5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46046</v>
       </c>
       <c r="D6" s="1">
         <v>46030</v>
       </c>
       <c r="E6" t="str">
-        <f>IF(COUNTIF(A:A, D6)&gt;0, "공휴일", IF(COUNTIF(B:B, D6)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F6">
-        <f>F7+1</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="G6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="H6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>48</v>
       </c>
       <c r="I6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46047</v>
       </c>
       <c r="D7" s="1">
         <v>46031</v>
       </c>
       <c r="E7" t="str">
-        <f>IF(COUNTIF(A:A, D7)&gt;0, "공휴일", IF(COUNTIF(B:B, D7)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F7">
-        <f>F8+1</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="G7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="H7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>47</v>
       </c>
       <c r="I7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46053</v>
       </c>
       <c r="D8" s="1">
         <v>46032</v>
       </c>
       <c r="E8" t="str">
-        <f>IF(COUNTIF(A:A, D8)&gt;0, "공휴일", IF(COUNTIF(B:B, D8)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>주말</v>
       </c>
       <c r="F8">
-        <f>F9+1</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="H8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>46</v>
       </c>
       <c r="I8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46054</v>
       </c>
       <c r="D9" s="1">
         <v>46033</v>
       </c>
       <c r="E9" t="str">
-        <f>IF(COUNTIF(A:A, D9)&gt;0, "공휴일", IF(COUNTIF(B:B, D9)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>주말</v>
       </c>
       <c r="F9">
-        <f>F10+1</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="G9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="H9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>45</v>
       </c>
       <c r="I9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46060</v>
       </c>
       <c r="D10" s="1">
         <v>46034</v>
       </c>
       <c r="E10" t="str">
-        <f>IF(COUNTIF(A:A, D10)&gt;0, "공휴일", IF(COUNTIF(B:B, D10)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F10">
-        <f>F11+1</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="G10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="H10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>44</v>
       </c>
       <c r="I10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46061</v>
       </c>
       <c r="D11" s="1">
         <v>46035</v>
       </c>
       <c r="E11" t="str">
-        <f>IF(COUNTIF(A:A, D11)&gt;0, "공휴일", IF(COUNTIF(B:B, D11)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F11">
-        <f>F12+1</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="G11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="H11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>43</v>
       </c>
       <c r="I11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46067</v>
       </c>
       <c r="D12" s="1">
         <v>46036</v>
       </c>
       <c r="E12" t="str">
-        <f>IF(COUNTIF(A:A, D12)&gt;0, "공휴일", IF(COUNTIF(B:B, D12)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F12">
-        <f>F13+1</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="G12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="H12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>42</v>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46068</v>
       </c>
       <c r="D13" s="1">
         <v>46037</v>
       </c>
       <c r="E13" t="str">
-        <f>IF(COUNTIF(A:A, D13)&gt;0, "공휴일", IF(COUNTIF(B:B, D13)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F13">
-        <f>F14+1</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="G13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="H13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>41</v>
       </c>
       <c r="I13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46074</v>
       </c>
       <c r="D14" s="1">
         <v>46038</v>
       </c>
       <c r="E14" t="str">
-        <f>IF(COUNTIF(A:A, D14)&gt;0, "공휴일", IF(COUNTIF(B:B, D14)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F14">
-        <f>F15+1</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="G14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="H14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="I14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46075</v>
       </c>
       <c r="D15" s="1">
         <v>46039</v>
       </c>
       <c r="E15" t="str">
-        <f>IF(COUNTIF(A:A, D15)&gt;0, "공휴일", IF(COUNTIF(B:B, D15)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>주말</v>
       </c>
       <c r="F15">
-        <f>F16+1</f>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="G15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="H15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>39</v>
       </c>
       <c r="I15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>46081</v>
       </c>
       <c r="D16" s="1">
         <v>46040</v>
       </c>
       <c r="E16" t="str">
-        <f>IF(COUNTIF(A:A, D16)&gt;0, "공휴일", IF(COUNTIF(B:B, D16)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>주말</v>
       </c>
       <c r="F16">
-        <f>F17+1</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="G16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="H16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="I16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -956,23 +956,23 @@
         <v>46041</v>
       </c>
       <c r="E17" t="str">
-        <f>IF(COUNTIF(A:A, D17)&gt;0, "공휴일", IF(COUNTIF(B:B, D17)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F17">
-        <f>F18+1</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="G17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="H17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>37</v>
       </c>
       <c r="I17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -981,23 +981,23 @@
         <v>46042</v>
       </c>
       <c r="E18" t="str">
-        <f>IF(COUNTIF(A:A, D18)&gt;0, "공휴일", IF(COUNTIF(B:B, D18)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F18">
-        <f>F19+1</f>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="G18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="H18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="I18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
     </row>
@@ -1006,23 +1006,23 @@
         <v>46043</v>
       </c>
       <c r="E19" t="str">
-        <f>IF(COUNTIF(A:A, D19)&gt;0, "공휴일", IF(COUNTIF(B:B, D19)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F19">
-        <f>F20+1</f>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="G19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="H19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="I19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
         <v>46044</v>
       </c>
       <c r="E20" t="str">
-        <f>IF(COUNTIF(A:A, D20)&gt;0, "공휴일", IF(COUNTIF(B:B, D20)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F20">
-        <f>F21+1</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="G20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="H20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>34</v>
       </c>
       <c r="I20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
     </row>
@@ -1056,23 +1056,23 @@
         <v>46045</v>
       </c>
       <c r="E21" t="str">
-        <f>IF(COUNTIF(A:A, D21)&gt;0, "공휴일", IF(COUNTIF(B:B, D21)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F21">
-        <f>F22+1</f>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="G21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="H21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>33</v>
       </c>
       <c r="I21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
     </row>
@@ -1081,23 +1081,23 @@
         <v>46046</v>
       </c>
       <c r="E22" t="str">
-        <f>IF(COUNTIF(A:A, D22)&gt;0, "공휴일", IF(COUNTIF(B:B, D22)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>주말</v>
       </c>
       <c r="F22">
-        <f>F23+1</f>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="G22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="H22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="I22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
     </row>
@@ -1106,23 +1106,23 @@
         <v>46047</v>
       </c>
       <c r="E23" t="str">
-        <f>IF(COUNTIF(A:A, D23)&gt;0, "공휴일", IF(COUNTIF(B:B, D23)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>주말</v>
       </c>
       <c r="F23">
-        <f>F24+1</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="G23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="H23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="I23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
     </row>
@@ -1131,23 +1131,23 @@
         <v>46048</v>
       </c>
       <c r="E24" t="str">
-        <f>IF(COUNTIF(A:A, D24)&gt;0, "공휴일", IF(COUNTIF(B:B, D24)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F24">
-        <f>F25+1</f>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="G24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="H24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="I24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
     </row>
@@ -1156,23 +1156,23 @@
         <v>46049</v>
       </c>
       <c r="E25" t="str">
-        <f>IF(COUNTIF(A:A, D25)&gt;0, "공휴일", IF(COUNTIF(B:B, D25)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F25">
-        <f>F26+1</f>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="G25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="H25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="I25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
     </row>
@@ -1181,23 +1181,23 @@
         <v>46050</v>
       </c>
       <c r="E26" t="str">
-        <f>IF(COUNTIF(A:A, D26)&gt;0, "공휴일", IF(COUNTIF(B:B, D26)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F26">
-        <f>F27+1</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="G26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="H26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="I26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
     </row>
@@ -1206,23 +1206,23 @@
         <v>46051</v>
       </c>
       <c r="E27" t="str">
-        <f>IF(COUNTIF(A:A, D27)&gt;0, "공휴일", IF(COUNTIF(B:B, D27)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F27">
-        <f>F28+1</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="G27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="H27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="I27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
     </row>
@@ -1231,23 +1231,23 @@
         <v>46052</v>
       </c>
       <c r="E28" t="str">
-        <f>IF(COUNTIF(A:A, D28)&gt;0, "공휴일", IF(COUNTIF(B:B, D28)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F28">
-        <f>F29+1</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="G28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="H28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="I28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
     </row>
@@ -1256,23 +1256,23 @@
         <v>46053</v>
       </c>
       <c r="E29" t="str">
-        <f>IF(COUNTIF(A:A, D29)&gt;0, "공휴일", IF(COUNTIF(B:B, D29)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>주말</v>
       </c>
       <c r="F29">
-        <f>F30+1</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="G29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="H29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
     </row>
@@ -1281,23 +1281,23 @@
         <v>46054</v>
       </c>
       <c r="E30" t="str">
-        <f>IF(COUNTIF(A:A, D30)&gt;0, "공휴일", IF(COUNTIF(B:B, D30)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>주말</v>
       </c>
       <c r="F30">
-        <f>F31+1</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="G30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="H30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="I30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
     </row>
@@ -1306,23 +1306,23 @@
         <v>46055</v>
       </c>
       <c r="E31" t="str">
-        <f>IF(COUNTIF(A:A, D31)&gt;0, "공휴일", IF(COUNTIF(B:B, D31)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F31">
-        <f>F32+1</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="G31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="H31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="I31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
     </row>
@@ -1331,23 +1331,23 @@
         <v>46056</v>
       </c>
       <c r="E32" t="str">
-        <f>IF(COUNTIF(A:A, D32)&gt;0, "공휴일", IF(COUNTIF(B:B, D32)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F32">
-        <f>F33+1</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="G32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="H32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="I32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
     </row>
@@ -1356,23 +1356,23 @@
         <v>46057</v>
       </c>
       <c r="E33" t="str">
-        <f>IF(COUNTIF(A:A, D33)&gt;0, "공휴일", IF(COUNTIF(B:B, D33)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="0"/>
         <v>평일</v>
       </c>
       <c r="F33">
-        <f>F34+1</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="G33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="H33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="I33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
     </row>
@@ -1381,23 +1381,23 @@
         <v>46058</v>
       </c>
       <c r="E34" t="str">
-        <f>IF(COUNTIF(A:A, D34)&gt;0, "공휴일", IF(COUNTIF(B:B, D34)&gt;0, "주말", "평일"))</f>
+        <f t="shared" ref="E34:E57" si="6">IF(COUNTIF(A:A, D34)&gt;0, "공휴일", IF(COUNTIF(B:B, D34)&gt;0, "주말", "평일"))</f>
         <v>평일</v>
       </c>
       <c r="F34">
-        <f>F35+1</f>
+        <f t="shared" ref="F34:F56" si="7">F35+1</f>
         <v>23</v>
       </c>
       <c r="G34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="H34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="I34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
     </row>
@@ -1406,23 +1406,23 @@
         <v>46059</v>
       </c>
       <c r="E35" t="str">
-        <f>IF(COUNTIF(A:A, D35)&gt;0, "공휴일", IF(COUNTIF(B:B, D35)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F35">
-        <f>F36+1</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="G35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="H35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="I35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -1431,23 +1431,23 @@
         <v>46060</v>
       </c>
       <c r="E36" t="str">
-        <f>IF(COUNTIF(A:A, D36)&gt;0, "공휴일", IF(COUNTIF(B:B, D36)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>주말</v>
       </c>
       <c r="F36">
-        <f>F37+1</f>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="G36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="H36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="I36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
     </row>
@@ -1456,23 +1456,23 @@
         <v>46061</v>
       </c>
       <c r="E37" t="str">
-        <f>IF(COUNTIF(A:A, D37)&gt;0, "공휴일", IF(COUNTIF(B:B, D37)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>주말</v>
       </c>
       <c r="F37">
-        <f>F38+1</f>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="G37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="H37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="I37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
         <v>46062</v>
       </c>
       <c r="E38" t="str">
-        <f>IF(COUNTIF(A:A, D38)&gt;0, "공휴일", IF(COUNTIF(B:B, D38)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F38">
-        <f>F39+1</f>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="G38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="H38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="I38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
     </row>
@@ -1506,23 +1506,23 @@
         <v>46063</v>
       </c>
       <c r="E39" t="str">
-        <f>IF(COUNTIF(A:A, D39)&gt;0, "공휴일", IF(COUNTIF(B:B, D39)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F39">
-        <f>F40+1</f>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="G39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="H39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="I39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
@@ -1531,23 +1531,23 @@
         <v>46064</v>
       </c>
       <c r="E40" t="str">
-        <f>IF(COUNTIF(A:A, D40)&gt;0, "공휴일", IF(COUNTIF(B:B, D40)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F40">
-        <f>F41+1</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="G40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="H40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="I40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
     </row>
@@ -1556,23 +1556,23 @@
         <v>46065</v>
       </c>
       <c r="E41" t="str">
-        <f>IF(COUNTIF(A:A, D41)&gt;0, "공휴일", IF(COUNTIF(B:B, D41)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F41">
-        <f>F42+1</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="G41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="H41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="I41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
     </row>
@@ -1581,23 +1581,23 @@
         <v>46066</v>
       </c>
       <c r="E42" t="str">
-        <f>IF(COUNTIF(A:A, D42)&gt;0, "공휴일", IF(COUNTIF(B:B, D42)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F42">
-        <f>F43+1</f>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="G42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="H42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="I42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
@@ -1606,23 +1606,23 @@
         <v>46067</v>
       </c>
       <c r="E43" t="str">
-        <f>IF(COUNTIF(A:A, D43)&gt;0, "공휴일", IF(COUNTIF(B:B, D43)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>주말</v>
       </c>
       <c r="F43">
-        <f>F44+1</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="G43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="H43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="I43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
     </row>
@@ -1631,23 +1631,23 @@
         <v>46068</v>
       </c>
       <c r="E44" t="str">
-        <f>IF(COUNTIF(A:A, D44)&gt;0, "공휴일", IF(COUNTIF(B:B, D44)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>주말</v>
       </c>
       <c r="F44">
-        <f>F45+1</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="G44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="H44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="I44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
     </row>
@@ -1656,23 +1656,23 @@
         <v>46069</v>
       </c>
       <c r="E45" t="str">
-        <f>IF(COUNTIF(A:A, D45)&gt;0, "공휴일", IF(COUNTIF(B:B, D45)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F45">
-        <f>F46+1</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="G45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="H45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="I45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
     </row>
@@ -1681,23 +1681,23 @@
         <v>46070</v>
       </c>
       <c r="E46" t="str">
-        <f>IF(COUNTIF(A:A, D46)&gt;0, "공휴일", IF(COUNTIF(B:B, D46)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>공휴일</v>
       </c>
       <c r="F46">
-        <f>F47+1</f>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="G46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="H46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="I46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
@@ -1706,23 +1706,23 @@
         <v>46071</v>
       </c>
       <c r="E47" t="str">
-        <f>IF(COUNTIF(A:A, D47)&gt;0, "공휴일", IF(COUNTIF(B:B, D47)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>공휴일</v>
       </c>
       <c r="F47">
-        <f>F48+1</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="G47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="H47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="I47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
@@ -1731,23 +1731,23 @@
         <v>46072</v>
       </c>
       <c r="E48" t="str">
-        <f>IF(COUNTIF(A:A, D48)&gt;0, "공휴일", IF(COUNTIF(B:B, D48)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>공휴일</v>
       </c>
       <c r="F48">
-        <f>F49+1</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="G48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="H48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="I48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -1756,23 +1756,23 @@
         <v>46073</v>
       </c>
       <c r="E49" t="str">
-        <f>IF(COUNTIF(A:A, D49)&gt;0, "공휴일", IF(COUNTIF(B:B, D49)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F49">
-        <f>F50+1</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="G49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="H49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="I49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -1781,23 +1781,23 @@
         <v>46074</v>
       </c>
       <c r="E50" t="str">
-        <f>IF(COUNTIF(A:A, D50)&gt;0, "공휴일", IF(COUNTIF(B:B, D50)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>주말</v>
       </c>
       <c r="F50">
-        <f>F51+1</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="G50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="H50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="I50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -1806,23 +1806,23 @@
         <v>46075</v>
       </c>
       <c r="E51" t="str">
-        <f>IF(COUNTIF(A:A, D51)&gt;0, "공휴일", IF(COUNTIF(B:B, D51)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>주말</v>
       </c>
       <c r="F51">
-        <f>F52+1</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="G51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="H51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="I51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -1831,23 +1831,23 @@
         <v>46076</v>
       </c>
       <c r="E52" t="str">
-        <f>IF(COUNTIF(A:A, D52)&gt;0, "공휴일", IF(COUNTIF(B:B, D52)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F52">
-        <f>F53+1</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="G52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="H52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="I52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -1856,23 +1856,23 @@
         <v>46077</v>
       </c>
       <c r="E53" t="str">
-        <f>IF(COUNTIF(A:A, D53)&gt;0, "공휴일", IF(COUNTIF(B:B, D53)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F53">
-        <f>F54+1</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="G53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="H53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="I53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
@@ -1881,23 +1881,23 @@
         <v>46078</v>
       </c>
       <c r="E54" t="str">
-        <f>IF(COUNTIF(A:A, D54)&gt;0, "공휴일", IF(COUNTIF(B:B, D54)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F54">
-        <f>F55+1</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="G54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="H54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="I54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -1906,23 +1906,23 @@
         <v>46079</v>
       </c>
       <c r="E55" t="str">
-        <f>IF(COUNTIF(A:A, D55)&gt;0, "공휴일", IF(COUNTIF(B:B, D55)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F55">
-        <f>F56+1</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="G55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="H55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="I55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -1931,11 +1931,11 @@
         <v>46080</v>
       </c>
       <c r="E56" t="str">
-        <f>IF(COUNTIF(A:A, D56)&gt;0, "공휴일", IF(COUNTIF(B:B, D56)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>평일</v>
       </c>
       <c r="F56">
-        <f>F57+1</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G56">
@@ -1943,11 +1943,11 @@
         <v>1</v>
       </c>
       <c r="H56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
         <v>46081</v>
       </c>
       <c r="E57" t="str">
-        <f>IF(COUNTIF(A:A, D57)&gt;0, "공휴일", IF(COUNTIF(B:B, D57)&gt;0, "주말", "평일"))</f>
+        <f t="shared" si="6"/>
         <v>주말</v>
       </c>
       <c r="F57">
@@ -1980,16 +1980,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6AC53DF-165D-438D-AAE8-9A9D75FD71F1}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.125" customWidth="1"/>
     <col min="2" max="2" width="23.5" customWidth="1"/>
     <col min="4" max="4" width="22.75" customWidth="1"/>
     <col min="5" max="5" width="22.875" customWidth="1"/>
+    <col min="7" max="7" width="22.75" customWidth="1"/>
+    <col min="8" max="8" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -2002,8 +2004,14 @@
       <c r="E1" s="1">
         <v>46027</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2016,8 +2024,14 @@
       <c r="E2" s="1">
         <v>46081</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2032,8 +2046,15 @@
         <f>NETWORKDAYS.INTL(E1,E2, "0000000")</f>
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <f>NETWORKDAYS.INTL(H1,H2, "0000000")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2048,8 +2069,15 @@
         <f>NETWORKDAYS(E1,E2, Sheet1!A:A)</f>
         <v>37</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <f>NETWORKDAYS(H1,H2, Sheet1!A:A)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -2064,8 +2092,15 @@
         <f>NETWORKDAYS.INTL(E1,E2, "0000000", Sheet1!A:A)</f>
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <f>NETWORKDAYS.INTL(H1,H2, "0000000", Sheet1!A:A)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -2080,8 +2115,15 @@
         <f>NETWORKDAYS.INTL(E1,E2,1)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <f>NETWORKDAYS.INTL(H1,H2,1)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2096,8 +2138,15 @@
         <f>NETWORKDAYS.INTL(E1+1,E2, "0000000")</f>
         <v>54</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9">
+        <f>NETWORKDAYS.INTL(H1+1,H2, "0000000")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2112,8 +2161,15 @@
         <f>NETWORKDAYS(E1+1,E2, Sheet1!A:A)</f>
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <f>NETWORKDAYS(H1+1,H2, Sheet1!A:A)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -2128,8 +2184,15 @@
         <f>NETWORKDAYS.INTL(E1+1,E2, "0000000", Sheet1!A:A)</f>
         <v>51</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <f>NETWORKDAYS.INTL(H1+1,H2, "0000000", Sheet1!A:A)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -2144,8 +2207,15 @@
         <f>NETWORKDAYS.INTL(E1+1,E2,1)</f>
         <v>39</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <f>NETWORKDAYS.INTL(H1+1,H2,1)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
         <v>9</v>
       </c>
@@ -2153,7 +2223,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
       <c r="D15" t="s">
         <v>11</v>
@@ -2162,7 +2232,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
         <v>12</v>
       </c>
